--- a/data/checklists/nba/1991-92-SkyBox-Basketball.xlsx
+++ b/data/checklists/nba/1991-92-SkyBox-Basketball.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D648"/>
+  <dimension ref="A1:D674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11972,6 +11972,462 @@
       </c>
       <c r="D648" t="inlineStr"/>
     </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>USA Basketball</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Blister Inserts</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Stay in School</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr"/>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Blister Inserts</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Orlando All-Star</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr"/>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Blister Inserts</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Inside Stuff</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr"/>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Blister Inserts</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Magic Johnson / James Worthy</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Blister Inserts</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Joe Dumars / Isiah Thomas</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Blister Inserts</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Rex Chapman</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Dennis Rodman</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO SP</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Chris Mullin</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO SP</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Mitch Richmond</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Reggie Miller</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Charles Smith</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Magic Johnson</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>James Worthy</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Pooh Richardson</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Dennis Scott</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Hersey Hawkins</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Tom Chambers</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Clyde Drexler</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Kevin Duckworth</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Terry Porter</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Buck Williams</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Ricky Pierce</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Bernard King</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Prototypes - PROTO</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
